--- a/output/2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,6 @@
           <t>+385-1-2910-110</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Filtri aria per HVAC, cabine verniciatura, otprašivanje industriale. Verificato (fininfo.hr, tvrtke.hr).</t>
@@ -534,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -576,7 +575,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -618,7 +617,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -660,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -690,7 +689,6 @@
           <t>+385 1 2406242</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Linea prodotto dedicata a filtri per otprašivanje industriale (feltri poliestere), pagina prodotto confermata sul sito.</t>
@@ -698,7 +696,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
